--- a/Weekly_Paid_Payments_Krishi_Bills_September_2026/Purchase_list_Account Transfer from company_Date_From 05-09-2026 to 11-09-2026/Weekly_paid_payment_List _From_05-09-20256 to 11-09-2026.xlsx
+++ b/Weekly_Paid_Payments_Krishi_Bills_September_2026/Purchase_list_Account Transfer from company_Date_From 05-09-2026 to 11-09-2026/Weekly_paid_payment_List _From_05-09-20256 to 11-09-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_September_2026\Weekly_Paid_Payments_Krishi_Bills_September_2026\Purchase_list_Account Transfer from company_Date_From 05-09-2026 to 11-09-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D0FBD7-CB7E-4338-97A3-37F9570D3019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496F6B1B-C1B8-4899-AC0D-51C57003BC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{68E78659-9BFD-4944-9A50-DCADFD4AF0BA}"/>
   </bookViews>
